--- a/data/processed/1404-table5.xlsx
+++ b/data/processed/1404-table5.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hamidreza/Documents/AI-Projects/IranBudget/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C001B9-9907-044A-A2F2-5A70BA189FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112F6789-A32F-0540-9A34-D72C8F45255D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19460" yWindow="500" windowWidth="23740" windowHeight="20080" activeTab="3" xr2:uid="{A1C43625-39F6-5F48-97AB-0D07967D3E07}"/>
+    <workbookView xWindow="19460" yWindow="500" windowWidth="23740" windowHeight="20080" xr2:uid="{A1C43625-39F6-5F48-97AB-0D07967D3E07}"/>
   </bookViews>
   <sheets>
     <sheet name="1404" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="1404 aggregate" sheetId="2" r:id="rId2"/>
     <sheet name="1403" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1 (2)" sheetId="4" r:id="rId4"/>
+    <sheet name="1403 aggregate" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="231">
   <si>
     <t>قسمت اول: درآمد‌ها</t>
   </si>
@@ -685,15 +685,6 @@
     <t>اعتبارات متفرقه</t>
   </si>
   <si>
-    <t>امنیت</t>
-  </si>
-  <si>
-    <t>آموزش</t>
-  </si>
-  <si>
-    <t>ارشاد</t>
-  </si>
-  <si>
     <t>مالیات اشخاص حقوقی</t>
   </si>
   <si>
@@ -737,6 +728,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>‌درآمدهای حاصل از مالکیت دولت</t>
   </si>
 </sst>
 </file>
@@ -2760,7 +2754,7 @@
         <v>1499000</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>310520</v>
       </c>
@@ -2771,7 +2765,7 @@
         <v>800000000</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>310521</v>
       </c>
@@ -2782,7 +2776,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>310600</v>
       </c>
@@ -2793,7 +2787,7 @@
         <v>131500000</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>319601</v>
       </c>
@@ -2804,7 +2798,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>319602</v>
       </c>
@@ -2815,7 +2809,7 @@
         <v>31500000</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>310605</v>
       </c>
@@ -2826,7 +2820,7 @@
         <v>44000000</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>310606</v>
       </c>
@@ -2837,7 +2831,7 @@
         <v>31000000</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>310700</v>
       </c>
@@ -2848,7 +2842,7 @@
         <v>5410000000</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>310705</v>
       </c>
@@ -2859,7 +2853,7 @@
         <v>5410000000</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B170" s="2" t="s">
         <v>151</v>
       </c>
@@ -2867,11 +2861,11 @@
         <v>53834550000</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="B174"/>
       <c r="C174"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B175" s="2" t="s">
         <v>153</v>
       </c>
@@ -2879,11 +2873,8 @@
         <v>85591174</v>
       </c>
       <c r="D175" s="4"/>
-      <c r="E175" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B176" s="2" t="s">
         <v>154</v>
       </c>
@@ -2891,11 +2882,8 @@
         <v>2304855</v>
       </c>
       <c r="D176" s="1"/>
-      <c r="E176" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="177" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B177" s="2" t="s">
         <v>155</v>
       </c>
@@ -2903,11 +2891,8 @@
         <v>449509</v>
       </c>
       <c r="D177" s="1"/>
-      <c r="E177" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="178" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B178" s="2" t="s">
         <v>156</v>
       </c>
@@ -2915,11 +2900,8 @@
         <v>10934996</v>
       </c>
       <c r="D178" s="1"/>
-      <c r="E178" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="179" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B179" s="2" t="s">
         <v>157</v>
       </c>
@@ -2928,7 +2910,7 @@
       </c>
       <c r="D179" s="1"/>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B180" s="2" t="s">
         <v>158</v>
       </c>
@@ -2937,7 +2919,7 @@
       </c>
       <c r="D180" s="1"/>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B181" s="2" t="s">
         <v>159</v>
       </c>
@@ -2946,7 +2928,7 @@
       </c>
       <c r="D181" s="1"/>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B182" s="2" t="s">
         <v>160</v>
       </c>
@@ -2955,7 +2937,7 @@
       </c>
       <c r="D182" s="1"/>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B183" s="2" t="s">
         <v>161</v>
       </c>
@@ -2964,7 +2946,7 @@
       </c>
       <c r="D183" s="1"/>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B184" s="2" t="s">
         <v>162</v>
       </c>
@@ -2973,7 +2955,7 @@
       </c>
       <c r="D184" s="1"/>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B185" s="2" t="s">
         <v>163</v>
       </c>
@@ -2982,7 +2964,7 @@
       </c>
       <c r="D185" s="1"/>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B186" s="2" t="s">
         <v>164</v>
       </c>
@@ -2991,7 +2973,7 @@
       </c>
       <c r="D186" s="1"/>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B187" s="2" t="s">
         <v>165</v>
       </c>
@@ -3000,7 +2982,7 @@
       </c>
       <c r="D187" s="1"/>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B188" s="2" t="s">
         <v>166</v>
       </c>
@@ -3009,7 +2991,7 @@
       </c>
       <c r="D188" s="1"/>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B189" s="2" t="s">
         <v>167</v>
       </c>
@@ -3018,7 +3000,7 @@
       </c>
       <c r="D189" s="1"/>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B190" s="2" t="s">
         <v>168</v>
       </c>
@@ -3026,7 +3008,7 @@
         <v>60142091</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B191" s="2" t="s">
         <v>169</v>
       </c>
@@ -3035,7 +3017,7 @@
       </c>
       <c r="D191" s="4"/>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B192" s="2" t="s">
         <v>170</v>
       </c>
@@ -3670,7 +3652,7 @@
     </row>
     <row r="34" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B34" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C34" s="3">
         <v>8166508049</v>
@@ -3678,7 +3660,7 @@
     </row>
     <row r="35" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C35" s="3">
         <v>3223566661</v>
@@ -3686,7 +3668,7 @@
     </row>
     <row r="36" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3">
         <v>551716162</v>
@@ -3694,7 +3676,7 @@
     </row>
     <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B37" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C37" s="3">
         <v>2719050000</v>
@@ -3702,7 +3684,7 @@
     </row>
     <row r="38" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B38" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C38" s="3">
         <v>6466124306</v>
@@ -3710,7 +3692,7 @@
     </row>
     <row r="39" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C39" s="3">
         <v>117840000</v>
@@ -3718,7 +3700,7 @@
     </row>
     <row r="40" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B40" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C40" s="3">
         <v>1951827876</v>
@@ -3726,7 +3708,7 @@
     </row>
     <row r="41" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C41" s="3">
         <v>3142025220</v>
@@ -3734,7 +3716,7 @@
     </row>
     <row r="42" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C42" s="3">
         <v>359342000</v>
@@ -3742,7 +3724,7 @@
     </row>
     <row r="43" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B43" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C43" s="3">
         <v>2041219726</v>
@@ -3755,7 +3737,7 @@
     </row>
     <row r="45" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B45" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C45" s="3">
         <v>6045000000</v>
@@ -3763,7 +3745,7 @@
     </row>
     <row r="46" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B46" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C46" s="3">
         <v>3254582000</v>
@@ -3771,7 +3753,7 @@
     </row>
     <row r="47" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C47" s="3">
         <v>5498000</v>
@@ -3784,7 +3766,7 @@
     </row>
     <row r="49" spans="2:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B49" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C49" s="3">
         <v>15800250000</v>
@@ -4142,7 +4124,7 @@
         <v>150</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -4165,241 +4147,181 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3">
-        <v>28739220000</v>
-      </c>
+      <c r="B1" s="3"/>
     </row>
     <row r="2" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3">
-        <v>21126965178</v>
-      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3">
-        <v>8166508049</v>
-      </c>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3">
-        <v>3223566661</v>
-      </c>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="3">
-        <v>551716162</v>
-      </c>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="3">
-        <v>2719050000</v>
-      </c>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="3">
-        <v>6466124306</v>
-      </c>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="3">
-        <v>117840000</v>
-      </c>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="3">
-        <v>1951827876</v>
-      </c>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="3">
-        <v>999999000</v>
-      </c>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="3">
-        <v>32111589</v>
-      </c>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="3">
-        <v>919717287</v>
-      </c>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="3">
-        <v>3142025220</v>
-      </c>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C14" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="3">
-        <v>3080141035</v>
-      </c>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C15" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="3">
-        <v>61884185</v>
-      </c>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="3">
-        <v>359342000</v>
-      </c>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="3">
-        <v>2041219726</v>
-      </c>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="3">
-        <v>9305080000</v>
-      </c>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="3">
-        <v>9305080000</v>
-      </c>
+      <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C20" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="3">
-        <v>6045000000</v>
-      </c>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C21" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="3">
-        <v>3254582000</v>
-      </c>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C22" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="3">
-        <v>5498000</v>
-      </c>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B23" s="3">
-        <v>15800250000</v>
-      </c>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="3">
-        <v>15800250000</v>
-      </c>
+      <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C25" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="3">
-        <v>8100003000</v>
-      </c>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C26" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D26" s="3">
-        <v>10000</v>
-      </c>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C27" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D27" s="3">
-        <v>7237000</v>
-      </c>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C28" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D28" s="3">
-        <v>2151500000</v>
-      </c>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C29" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D29" s="3">
-        <v>131500000</v>
-      </c>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:4" ht="19" x14ac:dyDescent="0.35">
       <c r="C30" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="3">
-        <v>5410000000</v>
-      </c>
+      <c r="D30" s="3"/>
     </row>
     <row r="33" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
@@ -4408,7 +4330,7 @@
     </row>
     <row r="34" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B34" s="2" t="s">
-        <v>2</v>
+        <v>215</v>
       </c>
       <c r="C34" s="1">
         <v>4723804498</v>
@@ -4416,7 +4338,7 @@
     </row>
     <row r="35" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
-        <v>13</v>
+        <v>216</v>
       </c>
       <c r="C35" s="1">
         <v>1916253759</v>
@@ -4424,7 +4346,7 @@
     </row>
     <row r="36" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
-        <v>19</v>
+        <v>217</v>
       </c>
       <c r="C36" s="1">
         <v>404748310</v>
@@ -4432,7 +4354,7 @@
     </row>
     <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B37" s="2" t="s">
-        <v>28</v>
+        <v>218</v>
       </c>
       <c r="C37" s="1">
         <v>1470649449</v>
@@ -4440,7 +4362,7 @@
     </row>
     <row r="38" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B38" s="2" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="C38" s="1">
         <v>5320870015</v>
@@ -4448,7 +4370,7 @@
     </row>
     <row r="39" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="C39" s="1">
         <v>80000000</v>
@@ -4456,7 +4378,7 @@
     </row>
     <row r="40" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B40" s="2" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
       <c r="C40" s="1">
         <v>1749747688</v>
@@ -4464,7 +4386,7 @@
     </row>
     <row r="41" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
-        <v>78</v>
+        <v>222</v>
       </c>
       <c r="C41" s="1">
         <v>1966531398</v>
@@ -4472,7 +4394,7 @@
     </row>
     <row r="42" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B42" s="2" t="s">
-        <v>92</v>
+        <v>223</v>
       </c>
       <c r="C42" s="1">
         <v>266672409</v>
@@ -4480,7 +4402,7 @@
     </row>
     <row r="43" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B43" s="2" t="s">
-        <v>93</v>
+        <v>224</v>
       </c>
       <c r="C43" s="1">
         <v>830431474</v>
@@ -4493,7 +4415,7 @@
     </row>
     <row r="45" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B45" s="2" t="s">
-        <v>96</v>
+        <v>225</v>
       </c>
       <c r="C45" s="1">
         <v>5827430000</v>
@@ -4501,7 +4423,7 @@
     </row>
     <row r="46" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B46" s="2" t="s">
-        <v>104</v>
+        <v>226</v>
       </c>
       <c r="C46" s="1">
         <v>622290000</v>
@@ -4509,7 +4431,7 @@
     </row>
     <row r="47" spans="1:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
-        <v>123</v>
+        <v>227</v>
       </c>
       <c r="C47" s="1">
         <v>1000</v>
@@ -4522,10 +4444,10 @@
     </row>
     <row r="49" spans="2:3" ht="19" x14ac:dyDescent="0.35">
       <c r="B49" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C49" s="3">
-        <v>15800250000</v>
+        <v>228</v>
+      </c>
+      <c r="C49" s="1">
+        <v>3191970000</v>
       </c>
     </row>
   </sheetData>
